--- a/output/Data and Chart Outputs/puerto_rico_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/puerto_rico_power_generation_daily.xlsx
@@ -21,8 +21,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,12 +62,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -379,6 +380,18 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="5"/>
@@ -785,7 +798,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -800,7 +812,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -822,7 +833,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -897,7 +907,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -923,7 +933,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -949,7 +959,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -975,7 +985,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1001,7 +1011,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1027,7 +1037,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1053,7 +1063,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1079,7 +1089,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1105,7 +1115,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1131,7 +1141,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1157,7 +1167,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1183,7 +1193,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1209,7 +1219,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1235,7 +1245,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1261,7 +1271,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1287,7 +1297,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1313,7 +1323,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1339,7 +1349,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1365,7 +1375,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1391,7 +1401,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1417,7 +1427,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1443,7 +1453,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1469,7 +1479,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1495,7 +1505,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1521,7 +1531,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1547,7 +1557,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1573,7 +1583,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1599,7 +1609,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1625,7 +1635,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1651,7 +1661,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1677,7 +1687,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1703,7 +1713,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1729,7 +1739,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1755,7 +1765,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -1781,7 +1791,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -1807,7 +1817,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -1833,7 +1843,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -1859,7 +1869,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -1885,7 +1895,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -1911,7 +1921,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -1937,7 +1947,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -1963,7 +1973,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -1989,7 +1999,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2015,7 +2025,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2041,7 +2051,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2067,7 +2077,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2093,7 +2103,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2119,7 +2129,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2145,7 +2155,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2171,7 +2181,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2197,7 +2207,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2223,7 +2233,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2249,7 +2259,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2275,7 +2285,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2301,7 +2311,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2327,7 +2337,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2353,7 +2363,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2379,7 +2389,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2405,7 +2415,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2431,7 +2441,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2457,7 +2467,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2483,7 +2493,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2509,7 +2519,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2535,7 +2545,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2561,7 +2571,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2587,7 +2597,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2613,7 +2623,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">

--- a/output/Data and Chart Outputs/puerto_rico_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/puerto_rico_power_generation_daily.xlsx
@@ -21,8 +21,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,13 +62,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -798,6 +797,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -812,6 +812,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -833,6 +834,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -907,7 +909,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -933,7 +935,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -959,7 +961,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -985,7 +987,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1011,7 +1013,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1037,7 +1039,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1063,7 +1065,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1089,7 +1091,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1115,7 +1117,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1141,7 +1143,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1167,7 +1169,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1193,7 +1195,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1219,7 +1221,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1245,7 +1247,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1271,7 +1273,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1297,7 +1299,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1323,7 +1325,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1349,7 +1351,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1375,7 +1377,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1401,7 +1403,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1427,7 +1429,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1453,7 +1455,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1479,7 +1481,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1505,7 +1507,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1531,7 +1533,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1557,7 +1559,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1583,7 +1585,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1609,7 +1611,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1635,7 +1637,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1661,7 +1663,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1687,7 +1689,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1713,7 +1715,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1739,7 +1741,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1765,7 +1767,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -1791,7 +1793,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -1817,7 +1819,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -1843,7 +1845,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -1869,7 +1871,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -1895,7 +1897,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -1921,7 +1923,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -1947,7 +1949,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -1973,7 +1975,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -1999,7 +2001,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2025,7 +2027,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2051,7 +2053,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2077,7 +2079,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2103,7 +2105,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2129,7 +2131,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2155,7 +2157,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2181,7 +2183,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2207,7 +2209,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2233,7 +2235,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2259,7 +2261,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2285,7 +2287,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2311,7 +2313,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2337,7 +2339,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2363,7 +2365,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2389,7 +2391,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2415,7 +2417,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2441,7 +2443,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2467,7 +2469,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2493,7 +2495,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2519,7 +2521,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2545,7 +2547,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2571,7 +2573,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2597,7 +2599,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2623,7 +2625,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">

--- a/output/Data and Chart Outputs/puerto_rico_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/puerto_rico_power_generation_daily.xlsx
@@ -21,8 +21,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,12 +62,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -797,7 +798,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -812,7 +812,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -834,7 +833,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -909,7 +907,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -935,7 +933,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -961,7 +959,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -987,7 +985,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1013,7 +1011,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1039,7 +1037,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1065,7 +1063,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1091,7 +1089,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1117,7 +1115,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1143,7 +1141,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1169,7 +1167,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1195,7 +1193,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1221,7 +1219,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1247,7 +1245,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1273,7 +1271,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1299,7 +1297,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1325,7 +1323,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1351,7 +1349,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1377,7 +1375,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1403,7 +1401,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1429,7 +1427,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1455,7 +1453,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1481,7 +1479,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1507,7 +1505,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1533,7 +1531,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1559,7 +1557,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1585,7 +1583,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1611,7 +1609,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1637,7 +1635,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1663,7 +1661,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1689,7 +1687,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1715,7 +1713,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1741,7 +1739,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1767,7 +1765,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -1793,7 +1791,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -1819,7 +1817,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -1845,7 +1843,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -1871,7 +1869,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -1897,7 +1895,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -1923,7 +1921,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -1949,7 +1947,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -1975,7 +1973,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2001,7 +1999,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2027,7 +2025,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2053,7 +2051,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2079,7 +2077,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2105,7 +2103,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2131,7 +2129,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2157,7 +2155,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2183,7 +2181,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2209,7 +2207,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2235,7 +2233,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2261,7 +2259,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2287,7 +2285,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2313,7 +2311,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2339,7 +2337,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2365,7 +2363,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2391,7 +2389,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2417,7 +2415,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2443,7 +2441,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2469,7 +2467,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2495,7 +2493,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2521,7 +2519,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2547,7 +2545,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2573,7 +2571,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2599,7 +2597,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2625,7 +2623,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">

--- a/output/Data and Chart Outputs/puerto_rico_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/puerto_rico_power_generation_daily.xlsx
@@ -157,6 +157,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Puerto Rico power generation by type (EIA-923) (to Jul/26)</a:t>
             </a:r>
           </a:p>

--- a/output/Data and Chart Outputs/puerto_rico_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/puerto_rico_power_generation_daily.xlsx
@@ -21,8 +21,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,13 +62,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -158,7 +157,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Puerto Rico power generation by type (EIA-923) (to Jul/26)</a:t>
+              <a:t>Puerto Rico power generation by type (EIA-923) (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -188,12 +187,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$68</f>
+              <f>'Chart'!$B$2:$B$69</f>
             </numRef>
           </val>
         </ser>
@@ -216,12 +215,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$68</f>
+              <f>'Chart'!$C$2:$C$69</f>
             </numRef>
           </val>
         </ser>
@@ -244,12 +243,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$68</f>
+              <f>'Chart'!$D$2:$D$69</f>
             </numRef>
           </val>
         </ser>
@@ -272,12 +271,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$68</f>
+              <f>'Chart'!$E$2:$E$69</f>
             </numRef>
           </val>
         </ser>
@@ -300,12 +299,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$68</f>
+              <f>'Chart'!$F$2:$F$69</f>
             </numRef>
           </val>
         </ser>
@@ -328,12 +327,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$68</f>
+              <f>'Chart'!$G$2:$G$69</f>
             </numRef>
           </val>
         </ser>
@@ -356,12 +355,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$68</f>
+              <f>'Chart'!$H$2:$H$69</f>
             </numRef>
           </val>
         </ser>
@@ -799,6 +798,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -809,10 +809,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jan-2021 to Jul-2026: 67 months. EIA publishes about two months after month end. Utility-scale plants only (EIA-923); rooftop solar is not included.</t>
+          <t>Jan-2021 to Aug-2026: 68 months. EIA publishes about two months after month end. Utility-scale plants only (EIA-923); rooftop solar is not included.</t>
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -834,6 +835,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -859,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -908,7 +910,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -934,7 +936,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -960,7 +962,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -986,7 +988,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1012,7 +1014,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1038,7 +1040,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1064,7 +1066,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1090,7 +1092,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1116,7 +1118,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1142,7 +1144,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1168,7 +1170,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1194,7 +1196,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1220,7 +1222,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1246,7 +1248,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1272,7 +1274,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1298,7 +1300,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1324,7 +1326,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1350,7 +1352,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1376,7 +1378,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1402,7 +1404,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1428,7 +1430,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1454,7 +1456,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1480,7 +1482,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1506,7 +1508,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1532,7 +1534,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1558,7 +1560,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1584,7 +1586,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1610,7 +1612,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1636,7 +1638,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1662,7 +1664,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1688,7 +1690,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1714,7 +1716,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1740,7 +1742,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1766,7 +1768,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -1792,7 +1794,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -1818,7 +1820,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -1844,7 +1846,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -1870,7 +1872,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -1896,7 +1898,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -1922,7 +1924,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -1948,7 +1950,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -1974,7 +1976,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2000,7 +2002,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2026,7 +2028,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2052,7 +2054,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2078,7 +2080,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2104,7 +2106,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2130,7 +2132,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2156,7 +2158,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2182,7 +2184,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2208,7 +2210,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2234,7 +2236,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2260,7 +2262,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2286,7 +2288,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2312,7 +2314,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2338,7 +2340,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2364,7 +2366,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2390,7 +2392,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2416,7 +2418,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2442,7 +2444,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2468,7 +2470,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2494,14 +2496,14 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>556.0905</v>
+        <v>556.0899000000001</v>
       </c>
       <c r="D63" t="n">
         <v>12.402</v>
@@ -2516,11 +2518,11 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>377.2615</v>
+        <v>377.2621</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2546,7 +2548,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2572,7 +2574,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2598,7 +2600,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2624,7 +2626,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -2647,6 +2649,32 @@
       </c>
       <c r="H68" t="n">
         <v>605.7824000000001</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B69" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" t="n">
+        <v>716.8198000000001</v>
+      </c>
+      <c r="D69" t="n">
+        <v>25.919</v>
+      </c>
+      <c r="E69" t="n">
+        <v>17.8231</v>
+      </c>
+      <c r="F69" t="n">
+        <v>267.339</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>600.4442</v>
       </c>
     </row>
   </sheetData>
@@ -2661,7 +2689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4864,7 +4892,7 @@
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>556090.5</v>
+        <v>556089.9</v>
       </c>
       <c r="D63" t="n">
         <v>12402</v>
@@ -4879,7 +4907,7 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>377305.5</v>
+        <v>377306.1</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
@@ -5064,6 +5092,41 @@
       </c>
       <c r="K68" t="n">
         <v>1607536.5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B69" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" t="n">
+        <v>716819.8</v>
+      </c>
+      <c r="D69" t="n">
+        <v>25919</v>
+      </c>
+      <c r="E69" t="n">
+        <v>17823.1</v>
+      </c>
+      <c r="F69" t="n">
+        <v>267339</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>600456.2</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>-12</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1628345.2</v>
       </c>
     </row>
   </sheetData>
@@ -5077,7 +5140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O68"/>
+  <dimension ref="A1:O69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7723,9 +7786,6 @@
       <c r="H62" t="n">
         <v>567923.7000000001</v>
       </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
       <c r="J62" t="n">
         <v>-58</v>
       </c>
@@ -7756,7 +7816,7 @@
         <v>141620</v>
       </c>
       <c r="D63" t="n">
-        <v>52259.07</v>
+        <v>52259.67</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -7768,7 +7828,7 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>556090.5299999999</v>
+        <v>556089.92</v>
       </c>
       <c r="J63" t="n">
         <v>-44</v>
@@ -8006,6 +8066,50 @@
         <v>29736</v>
       </c>
       <c r="O68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B69" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" t="n">
+        <v>267339</v>
+      </c>
+      <c r="D69" t="n">
+        <v>169832.88</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>716819.76</v>
+      </c>
+      <c r="J69" t="n">
+        <v>-12</v>
+      </c>
+      <c r="K69" t="n">
+        <v>430623.36</v>
+      </c>
+      <c r="L69" t="n">
+        <v>17823.15</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>25919</v>
+      </c>
+      <c r="O69" t="n">
         <v>0</v>
       </c>
     </row>
